--- a/e2e/expectedData/Non_Regular_Salary_BFKJ_Q1.xlsx
+++ b/e2e/expectedData/Non_Regular_Salary_BFKJ_Q1.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="51">
   <si>
     <t>DAFTAR PEMBAYARAN</t>
   </si>
@@ -62,39 +62,48 @@
     <t>MAR</t>
   </si>
   <si>
+    <t>ADROALDINO DA SILVA NORONHA TOME</t>
+  </si>
+  <si>
+    <t>VI</t>
+  </si>
+  <si>
+    <t>Expat</t>
+  </si>
+  <si>
+    <t>0,00</t>
+  </si>
+  <si>
+    <t>550,00</t>
+  </si>
+  <si>
+    <t>1.100,00</t>
+  </si>
+  <si>
+    <t>110,00</t>
+  </si>
+  <si>
     <t>CELIA MARIA REGO DE FATIMA</t>
   </si>
   <si>
     <t>IV</t>
   </si>
   <si>
-    <t>Expat</t>
-  </si>
-  <si>
-    <t>550,00</t>
+    <t>Local</t>
   </si>
   <si>
     <t>1.650,00</t>
   </si>
   <si>
+    <t>115,00</t>
+  </si>
+  <si>
+    <t>AHMAD RIYANA SAPUTRA</t>
+  </si>
+  <si>
     <t>165,00</t>
   </si>
   <si>
-    <t>ADROALDINO DA SILVA NORONHA TOME</t>
-  </si>
-  <si>
-    <t>VI</t>
-  </si>
-  <si>
-    <t>0,00</t>
-  </si>
-  <si>
-    <t>1.100,00</t>
-  </si>
-  <si>
-    <t>110,00</t>
-  </si>
-  <si>
     <t>HERU YULIANTO</t>
   </si>
   <si>
@@ -104,21 +113,18 @@
     <t>Homestaff</t>
   </si>
   <si>
-    <t>AHMAD RIYANA SAPUTRA</t>
+    <t>AGOSTINHO GOMES FERNANDES</t>
+  </si>
+  <si>
+    <t>100,00</t>
+  </si>
+  <si>
+    <t>300,00</t>
   </si>
   <si>
     <t>RIMBUN SIBURIAN</t>
   </si>
   <si>
-    <t>100,00</t>
-  </si>
-  <si>
-    <t>300,00</t>
-  </si>
-  <si>
-    <t>AGOSTINHO GOMES FERNANDES</t>
-  </si>
-  <si>
     <t>SYALDY KHARISMA ANANDA</t>
   </si>
   <si>
@@ -134,7 +140,10 @@
     <t>6.300,00</t>
   </si>
   <si>
-    <t>DILI, 26 August 2026</t>
+    <t>500,00</t>
+  </si>
+  <si>
+    <t>DILI, 09 September 2026</t>
   </si>
   <si>
     <t>PREPARED BY</t>
@@ -656,7 +665,7 @@
     </row>
     <row r="7" spans="1:11">
       <c r="A7" s="3">
-        <v>92003</v>
+        <v>24016</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>15</v>
@@ -672,126 +681,126 @@
       </c>
       <c r="F7" s="3"/>
       <c r="G7" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I7" s="3" t="s">
         <v>18</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="8" spans="1:11">
       <c r="A8" s="3">
-        <v>24016</v>
+        <v>92003</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F8" s="3"/>
       <c r="G8" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="9" spans="1:11">
       <c r="A9" s="3">
-        <v>74003</v>
+        <v>95008</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F9" s="3"/>
       <c r="G9" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
     <row r="10" spans="1:11">
       <c r="A10" s="3">
-        <v>95008</v>
+        <v>74003</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>18</v>
       </c>
       <c r="F10" s="3"/>
       <c r="G10" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I10" s="3" t="s">
         <v>18</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="11" spans="1:11">
       <c r="A11" s="3">
-        <v>81010</v>
+        <v>26013</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>16</v>
@@ -800,56 +809,56 @@
         <v>17</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F11" s="3"/>
       <c r="G11" s="3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
     </row>
     <row r="12" spans="1:11">
       <c r="A12" s="3">
-        <v>26013</v>
+        <v>81010</v>
       </c>
       <c r="B12" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E12" s="3" t="s">
         <v>33</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>31</v>
       </c>
       <c r="F12" s="3"/>
       <c r="G12" s="3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -857,37 +866,37 @@
         <v>91015</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="F13" s="3"/>
       <c r="G13" s="3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
     </row>
     <row r="14" spans="1:11">
       <c r="A14" s="4" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
@@ -898,10 +907,10 @@
       <c r="H14" s="3"/>
       <c r="I14" s="3"/>
       <c r="J14" s="4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="K14" s="4" t="s">
-        <v>18</v>
+        <v>41</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -909,20 +918,20 @@
     </row>
     <row r="16" spans="1:11">
       <c r="A16" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="G16"/>
     </row>
     <row r="17" spans="1:11">
       <c r="A17" s="5" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B17" s="5"/>
       <c r="C17" s="5"/>
       <c r="D17" s="5"/>
       <c r="E17" s="5"/>
       <c r="F17" s="5" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="G17" s="5"/>
       <c r="H17" s="5"/>
@@ -932,11 +941,11 @@
     </row>
     <row r="18" spans="1:11">
       <c r="A18" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="E18"/>
       <c r="H18" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
     </row>
     <row r="19" spans="1:11" customHeight="1" ht="37.5">
@@ -946,20 +955,20 @@
     </row>
     <row r="20" spans="1:11">
       <c r="A20" s="1" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="E20"/>
       <c r="H20" s="1" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="21" spans="1:11">
       <c r="A21" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="E21"/>
       <c r="H21" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>

--- a/e2e/expectedData/Non_Regular_Salary_BFKJ_Q1.xlsx
+++ b/e2e/expectedData/Non_Regular_Salary_BFKJ_Q1.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="52">
   <si>
     <t>DAFTAR PEMBAYARAN</t>
   </si>
@@ -68,39 +68,42 @@
     <t>VI</t>
   </si>
   <si>
+    <t>Outsource</t>
+  </si>
+  <si>
+    <t>0,00</t>
+  </si>
+  <si>
+    <t>550,00</t>
+  </si>
+  <si>
+    <t>1.100,00</t>
+  </si>
+  <si>
+    <t>110,00</t>
+  </si>
+  <si>
+    <t>CELIA MARIA REGO DE FATIMA</t>
+  </si>
+  <si>
+    <t>IV</t>
+  </si>
+  <si>
+    <t>Local</t>
+  </si>
+  <si>
+    <t>1.650,00</t>
+  </si>
+  <si>
+    <t>115,00</t>
+  </si>
+  <si>
+    <t>AHMAD RIYANA SAPUTRA</t>
+  </si>
+  <si>
     <t>Expat</t>
   </si>
   <si>
-    <t>0,00</t>
-  </si>
-  <si>
-    <t>550,00</t>
-  </si>
-  <si>
-    <t>1.100,00</t>
-  </si>
-  <si>
-    <t>110,00</t>
-  </si>
-  <si>
-    <t>CELIA MARIA REGO DE FATIMA</t>
-  </si>
-  <si>
-    <t>IV</t>
-  </si>
-  <si>
-    <t>Local</t>
-  </si>
-  <si>
-    <t>1.650,00</t>
-  </si>
-  <si>
-    <t>115,00</t>
-  </si>
-  <si>
-    <t>AHMAD RIYANA SAPUTRA</t>
-  </si>
-  <si>
     <t>165,00</t>
   </si>
   <si>
@@ -143,7 +146,7 @@
     <t>500,00</t>
   </si>
   <si>
-    <t>DILI, 09 September 2026</t>
+    <t>DILI, 10 September 2026</t>
   </si>
   <si>
     <t>PREPARED BY</t>
@@ -740,7 +743,7 @@
         <v>23</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>19</v>
@@ -759,7 +762,7 @@
         <v>25</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -767,13 +770,13 @@
         <v>74003</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>18</v>
@@ -800,29 +803,29 @@
         <v>26013</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>16</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F11" s="3"/>
       <c r="G11" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K11" s="3" t="s">
         <v>18</v>
@@ -833,7 +836,7 @@
         <v>81010</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>23</v>
@@ -842,20 +845,20 @@
         <v>24</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F12" s="3"/>
       <c r="G12" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K12" s="3" t="s">
         <v>18</v>
@@ -866,29 +869,29 @@
         <v>91015</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>18</v>
       </c>
       <c r="F13" s="3"/>
       <c r="G13" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I13" s="3" t="s">
         <v>18</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K13" s="3" t="s">
         <v>18</v>
@@ -896,7 +899,7 @@
     </row>
     <row r="14" spans="1:11">
       <c r="A14" s="4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
@@ -907,10 +910,10 @@
       <c r="H14" s="3"/>
       <c r="I14" s="3"/>
       <c r="J14" s="4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K14" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -918,20 +921,20 @@
     </row>
     <row r="16" spans="1:11">
       <c r="A16" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G16"/>
     </row>
     <row r="17" spans="1:11">
       <c r="A17" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B17" s="5"/>
       <c r="C17" s="5"/>
       <c r="D17" s="5"/>
       <c r="E17" s="5"/>
       <c r="F17" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G17" s="5"/>
       <c r="H17" s="5"/>
@@ -941,11 +944,11 @@
     </row>
     <row r="18" spans="1:11">
       <c r="A18" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E18"/>
       <c r="H18" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="19" spans="1:11" customHeight="1" ht="37.5">
@@ -955,20 +958,20 @@
     </row>
     <row r="20" spans="1:11">
       <c r="A20" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E20"/>
       <c r="H20" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="21" spans="1:11">
       <c r="A21" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E21"/>
       <c r="H21" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
   </sheetData>
